--- a/artfynd/A 46969-2023 artfynd.xlsx
+++ b/artfynd/A 46969-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46969-2023 artfynd.xlsx
+++ b/artfynd/A 46969-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118765519</v>
+        <v>118765857</v>
       </c>
       <c r="B3" t="n">
-        <v>97880</v>
+        <v>103361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>224416</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694046</v>
+        <v>694086</v>
       </c>
       <c r="R3" t="n">
-        <v>6382536</v>
+        <v>6382569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118765969</v>
+        <v>118765519</v>
       </c>
       <c r="B4" t="n">
-        <v>106120</v>
+        <v>97880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,38 +905,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694092</v>
+        <v>694046</v>
       </c>
       <c r="R4" t="n">
-        <v>6382560</v>
+        <v>6382536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +992,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1007,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118765857</v>
+        <v>118765520</v>
       </c>
       <c r="B5" t="n">
-        <v>103361</v>
+        <v>97880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,34 +1015,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694086</v>
+        <v>694036</v>
       </c>
       <c r="R5" t="n">
-        <v>6382569</v>
+        <v>6382519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1102,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1109,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118765520</v>
+        <v>118765969</v>
       </c>
       <c r="B6" t="n">
-        <v>97880</v>
+        <v>106120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,42 +1125,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>221849</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694036</v>
+        <v>694092</v>
       </c>
       <c r="R6" t="n">
-        <v>6382519</v>
+        <v>6382560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 46969-2023 artfynd.xlsx
+++ b/artfynd/A 46969-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118765857</v>
+        <v>118765969</v>
       </c>
       <c r="B3" t="n">
-        <v>103361</v>
+        <v>106120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,19 +807,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224416</v>
+        <v>221849</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694086</v>
+        <v>694092</v>
       </c>
       <c r="R3" t="n">
-        <v>6382569</v>
+        <v>6382560</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118765519</v>
+        <v>118765520</v>
       </c>
       <c r="B4" t="n">
         <v>97880</v>
@@ -937,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694046</v>
+        <v>694036</v>
       </c>
       <c r="R4" t="n">
-        <v>6382536</v>
+        <v>6382519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118765520</v>
+        <v>118765519</v>
       </c>
       <c r="B5" t="n">
         <v>97880</v>
@@ -1047,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694036</v>
+        <v>694046</v>
       </c>
       <c r="R5" t="n">
-        <v>6382519</v>
+        <v>6382536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118765969</v>
+        <v>118765857</v>
       </c>
       <c r="B6" t="n">
-        <v>106120</v>
+        <v>103361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,23 +1133,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>224416</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694092</v>
+        <v>694086</v>
       </c>
       <c r="R6" t="n">
-        <v>6382560</v>
+        <v>6382569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46969-2023 artfynd.xlsx
+++ b/artfynd/A 46969-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>118765969</v>
       </c>
       <c r="B3" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118765520</v>
+        <v>118765857</v>
       </c>
       <c r="B4" t="n">
-        <v>97880</v>
+        <v>103368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,42 +909,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694036</v>
+        <v>694086</v>
       </c>
       <c r="R4" t="n">
-        <v>6382519</v>
+        <v>6382569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +988,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1007,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118765519</v>
+        <v>118765520</v>
       </c>
       <c r="B5" t="n">
-        <v>97880</v>
+        <v>97887</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694046</v>
+        <v>694036</v>
       </c>
       <c r="R5" t="n">
-        <v>6382536</v>
+        <v>6382519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118765857</v>
+        <v>118765519</v>
       </c>
       <c r="B6" t="n">
-        <v>103361</v>
+        <v>97887</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,34 +1121,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224416</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694086</v>
+        <v>694046</v>
       </c>
       <c r="R6" t="n">
-        <v>6382569</v>
+        <v>6382536</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 46969-2023 artfynd.xlsx
+++ b/artfynd/A 46969-2023 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118765969</v>
+        <v>118765519</v>
       </c>
       <c r="B3" t="n">
-        <v>106127</v>
+        <v>97887</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694092</v>
+        <v>694046</v>
       </c>
       <c r="R3" t="n">
-        <v>6382560</v>
+        <v>6382536</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118765857</v>
+        <v>118765520</v>
       </c>
       <c r="B4" t="n">
-        <v>103368</v>
+        <v>97887</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +913,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694086</v>
+        <v>694036</v>
       </c>
       <c r="R4" t="n">
-        <v>6382569</v>
+        <v>6382519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +1000,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Kaj Svahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -999,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118765520</v>
+        <v>118765969</v>
       </c>
       <c r="B5" t="n">
-        <v>97887</v>
+        <v>106127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,42 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694036</v>
+        <v>694092</v>
       </c>
       <c r="R5" t="n">
-        <v>6382519</v>
+        <v>6382560</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1106,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1109,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118765519</v>
+        <v>118765857</v>
       </c>
       <c r="B6" t="n">
-        <v>97887</v>
+        <v>103368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,42 +1129,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>224416</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694046</v>
+        <v>694086</v>
       </c>
       <c r="R6" t="n">
-        <v>6382536</v>
+        <v>6382569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kaj Svahn</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
